--- a/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,73</t>
+          <t>0,47; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,92</t>
+          <t>1,28; 4,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,69</t>
+          <t>0,63; 3,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,27</t>
+          <t>0,98; 5,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,39</t>
+          <t>0,28; 2,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,62</t>
+          <t>1,53; 4,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,92</t>
+          <t>0,41; 1,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,87</t>
+          <t>0,93; 2,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,66</t>
+          <t>1,57; 3,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,81</t>
+          <t>0,23; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,74</t>
+          <t>0,98; 5,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,91</t>
+          <t>0,24; 2,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,38</t>
+          <t>0,79; 3,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,1</t>
+          <t>0,25; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,53</t>
+          <t>0,54; 3,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,63</t>
+          <t>1,35; 3,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,86</t>
+          <t>0,27; 1,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,97</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,53</t>
+          <t>0,51; 2,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,95</t>
+          <t>1,31; 2,97</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,49</t>
+          <t>0,17; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,63</t>
+          <t>1,51; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,86</t>
+          <t>0,19; 1,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,57</t>
+          <t>0,28; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,06</t>
+          <t>0,36; 3,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,33</t>
+          <t>0,7; 4,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,48</t>
+          <t>0,27; 1,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,55</t>
+          <t>1,3; 3,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,61</t>
+          <t>0,27; 1,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,51</t>
+          <t>0,44; 2,5</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,67</t>
+          <t>0,52; 1,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,09</t>
+          <t>0,62; 1,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,9</t>
+          <t>1,29; 2,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,51</t>
+          <t>0,72; 2,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,68</t>
+          <t>1,42; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,55</t>
+          <t>0,84; 2,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 59,9</t>
+          <t>2,08; 52,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,64</t>
+          <t>0,68; 1,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,36</t>
+          <t>1,1; 2,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,45</t>
+          <t>0,57; 1,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 37,48</t>
+          <t>2,0; 40,83</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,36</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,72</t>
+          <t>0,58; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,33</t>
+          <t>0,9; 3,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,49</t>
+          <t>1,49; 4,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,69</t>
+          <t>0,16; 1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,45</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,3</t>
+          <t>1,61; 4,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,53</t>
+          <t>1,69; 3,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,3</t>
+          <t>0,28; 1,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,28</t>
+          <t>1,59; 3,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,48</t>
+          <t>1,59; 3,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,66</t>
+          <t>1,93; 3,61</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,63</t>
+          <t>0,75; 4,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,33</t>
+          <t>1,9; 7,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,04</t>
+          <t>0,68; 4,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,75</t>
+          <t>1,27; 7,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,07</t>
+          <t>0,75; 2,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,91</t>
+          <t>1,26; 2,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,29</t>
+          <t>0,74; 2,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,98</t>
+          <t>2,53; 4,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,25</t>
+          <t>0,95; 2,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,35</t>
+          <t>1,59; 3,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,22</t>
+          <t>0,9; 2,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,85</t>
+          <t>2,42; 4,67</t>
         </is>
       </c>
     </row>
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,31</t>
+          <t>0,61; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,44</t>
+          <t>1,41; 2,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,35</t>
+          <t>0,62; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,61</t>
+          <t>0,83; 1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,71</t>
+          <t>1,64; 2,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,14</t>
+          <t>1,25; 2,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 25,39</t>
+          <t>2,56; 25,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,81; 1,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,36</t>
+          <t>1,64; 2,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,57</t>
+          <t>1,03; 1,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 15,03</t>
+          <t>2,26; 15,3</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6226</t>
+          <t>0; 6122</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2079; 11923</t>
+          <t>2035; 11029</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5139</t>
+          <t>0; 5461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6345; 19824</t>
+          <t>6446; 20790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1926; 11317</t>
+          <t>1927; 11902</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3193; 16567</t>
+          <t>3095; 16184</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>995; 8311</t>
+          <t>988; 9426</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6283; 20663</t>
+          <t>6851; 20263</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3190; 14954</t>
+          <t>3181; 14538</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7032; 21580</t>
+          <t>6976; 22038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1204; 10777</t>
+          <t>1214; 11329</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15224; 34837</t>
+          <t>14955; 34214</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>813; 10300</t>
+          <t>826; 9808</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4191; 19849</t>
+          <t>4099; 22364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>891; 10961</t>
+          <t>906; 10291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3462; 15305</t>
+          <t>3582; 15426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>932; 7820</t>
+          <t>939; 8931</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6356</t>
+          <t>0; 7441</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1964; 13125</t>
+          <t>2007; 14299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5067; 13904</t>
+          <t>5172; 14104</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2538; 13742</t>
+          <t>2014; 13604</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6052; 22489</t>
+          <t>5886; 23852</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3994; 18989</t>
+          <t>3834; 18041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10917; 24658</t>
+          <t>10915; 24762</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>909; 8070</t>
+          <t>911; 7716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9237; 29163</t>
+          <t>9519; 29483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1001; 9725</t>
+          <t>996; 9655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2102; 17194</t>
+          <t>1885; 17156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6786</t>
+          <t>0; 6792</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>933; 7957</t>
+          <t>944; 8813</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5332</t>
+          <t>0; 5447</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1185; 7235</t>
+          <t>1170; 6960</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1871; 10491</t>
+          <t>1913; 10850</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11475; 31568</t>
+          <t>11562; 32612</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1909; 11108</t>
+          <t>1836; 10702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3709; 20957</t>
+          <t>3641; 20880</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6368; 20673</t>
+          <t>6419; 20996</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8009; 24176</t>
+          <t>7133; 21652</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2820; 13464</t>
+          <t>2899; 13462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13292; 30058</t>
+          <t>13318; 30383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5018; 17955</t>
+          <t>5125; 18736</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10845; 28193</t>
+          <t>10851; 29031</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6947; 21064</t>
+          <t>6897; 20434</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21120; 585908</t>
+          <t>20335; 517339</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14271; 32041</t>
+          <t>13236; 34040</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22189; 45507</t>
+          <t>21229; 44336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11826; 28639</t>
+          <t>11260; 28549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39435; 754498</t>
+          <t>40187; 821809</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>820; 8285</t>
+          <t>0; 7236</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2983; 13884</t>
+          <t>2974; 13995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6041; 20647</t>
+          <t>5568; 20112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7529; 21323</t>
+          <t>7087; 20492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>897; 9614</t>
+          <t>897; 9687</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14179; 33850</t>
+          <t>14715; 34567</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12258; 31723</t>
+          <t>11921; 31392</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14598; 29697</t>
+          <t>14226; 30871</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2266; 11966</t>
+          <t>2568; 12701</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19440; 41677</t>
+          <t>20200; 41290</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22422; 47244</t>
+          <t>21650; 46870</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25838; 48135</t>
+          <t>25352; 47538</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2639; 13815</t>
+          <t>2233; 14637</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4939; 19562</t>
+          <t>5081; 20488</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1959; 11588</t>
+          <t>1950; 11660</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2667; 18628</t>
+          <t>3066; 17692</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8814; 25861</t>
+          <t>9313; 26892</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12871; 32260</t>
+          <t>13972; 32823</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8135; 24739</t>
+          <t>7978; 26060</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19149; 37910</t>
+          <t>19276; 37041</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14953; 34786</t>
+          <t>14671; 33879</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22153; 46035</t>
+          <t>21900; 47611</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11555; 30421</t>
+          <t>12375; 30903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24752; 48585</t>
+          <t>24203; 46742</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20339; 42908</t>
+          <t>20049; 44031</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48357; 83350</t>
+          <t>48389; 82285</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20916; 45716</t>
+          <t>21104; 44675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49553; 87545</t>
+          <t>49750; 87329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28003; 54426</t>
+          <t>28013; 53119</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58073; 96167</t>
+          <t>58304; 92849</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42674; 75702</t>
+          <t>43997; 75424</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>92426; 908487</t>
+          <t>91441; 916920</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54551; 87263</t>
+          <t>53805; 86878</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115392; 164530</t>
+          <t>114187; 162529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70925; 108298</t>
+          <t>70909; 110291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>157509; 1045243</t>
+          <t>156972; 1064040</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,52</t>
+          <t>0,47; 2,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,12</t>
+          <t>1,26; 3,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,88</t>
+          <t>0,66; 3,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,15</t>
+          <t>1,2; 5,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,72</t>
+          <t>0,28; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,53</t>
+          <t>1,43; 4,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,86</t>
+          <t>0,4; 1,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,93</t>
+          <t>0,83; 2,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,15; 1,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,59</t>
+          <t>1,62; 3,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,67</t>
+          <t>0,23; 2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,34</t>
+          <t>0,94; 4,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,73</t>
+          <t>0,24; 3,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,41</t>
+          <t>0,79; 3,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,4</t>
+          <t>0,25; 2,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,84</t>
+          <t>0,53; 3,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,69</t>
+          <t>1,46; 3,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,84</t>
+          <t>0,35; 1,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,75; 3,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,41</t>
+          <t>0,53; 2,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,97</t>
+          <t>1,28; 2,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,42</t>
+          <t>0,17; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,68</t>
+          <t>1,44; 4,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,85</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,57</t>
+          <t>0,91; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,39</t>
+          <t>0,36; 2,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,17</t>
+          <t>0,71; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,53</t>
+          <t>0,26; 1,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,67</t>
+          <t>1,32; 3,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,56</t>
+          <t>0,26; 1,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,5</t>
+          <t>1,0; 2,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,7</t>
+          <t>0,49; 1,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,87</t>
+          <t>0,67; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,17</t>
+          <t>0,25; 1,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,94</t>
+          <t>1,29; 2,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,62</t>
+          <t>0,7; 2,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,79</t>
+          <t>1,4; 3,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,47</t>
+          <t>0,79; 2,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 52,89</t>
+          <t>1,7; 3,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,74</t>
+          <t>0,68; 1,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,3</t>
+          <t>1,14; 2,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,45</t>
+          <t>0,6; 1,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 40,83</t>
+          <t>1,63; 2,84</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,23; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,74</t>
+          <t>0,58; 2,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,24</t>
+          <t>0,86; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,31</t>
+          <t>1,49; 4,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,7</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,81; 4,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,25</t>
+          <t>1,67; 4,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,67</t>
+          <t>2,12; 3,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,38</t>
+          <t>0,24; 1,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,25</t>
+          <t>1,61; 3,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,45</t>
+          <t>1,55; 3,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,61</t>
+          <t>2,12; 3,76</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,91</t>
+          <t>1,01; 4,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,68</t>
+          <t>1,97; 8,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,06</t>
+          <t>0,65; 3,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 7,36</t>
+          <t>2,08; 9,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,15</t>
+          <t>0,74; 2,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,96</t>
+          <t>1,18; 2,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,41</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,87</t>
+          <t>2,63; 5,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,19</t>
+          <t>0,9; 2,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,46</t>
+          <t>1,63; 3,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,26</t>
+          <t>0,89; 2,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,67</t>
+          <t>2,74; 5,29</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,35</t>
+          <t>0,59; 1,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,4</t>
+          <t>1,42; 2,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,32</t>
+          <t>0,63; 1,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,59</t>
+          <t>1,76; 2,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,57</t>
+          <t>0,83; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,62</t>
+          <t>1,65; 2,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,14</t>
+          <t>1,25; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 25,63</t>
+          <t>2,38; 3,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,31</t>
+          <t>0,82; 1,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,33</t>
+          <t>1,65; 2,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,59</t>
+          <t>1,03; 1,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 15,3</t>
+          <t>2,21; 2,93</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>25256</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6122</t>
+          <t>0; 7763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2035; 11029</t>
+          <t>2051; 11319</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5461</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6446; 20790</t>
+          <t>6921; 21825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1927; 11902</t>
+          <t>2012; 11471</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3095; 16184</t>
+          <t>3786; 17483</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>988; 9426</t>
+          <t>985; 8918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6851; 20263</t>
+          <t>6962; 20300</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3181; 14538</t>
+          <t>3137; 14810</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6976; 22038</t>
+          <t>6247; 21580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1214; 11329</t>
+          <t>1198; 10642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14955; 34214</t>
+          <t>16805; 38294</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>18327</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>826; 9808</t>
+          <t>827; 9943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4099; 22364</t>
+          <t>3942; 20796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>906; 10291</t>
+          <t>912; 11384</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3582; 15426</t>
+          <t>3841; 15188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>939; 8931</t>
+          <t>933; 8502</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7441</t>
+          <t>0; 7412</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2007; 14299</t>
+          <t>1982; 13303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5172; 14104</t>
+          <t>6179; 16463</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2014; 13604</t>
+          <t>2562; 13013</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5886; 23852</t>
+          <t>5655; 23656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3834; 18041</t>
+          <t>3987; 19161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10915; 24762</t>
+          <t>11606; 26733</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12032</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>911; 7716</t>
+          <t>915; 8041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9519; 29483</t>
+          <t>9054; 28788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>996; 9655</t>
+          <t>1000; 9599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1885; 17156</t>
+          <t>4302; 15549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6792</t>
+          <t>0; 6737</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>944; 8813</t>
+          <t>941; 7008</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5447</t>
+          <t>0; 5509</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1170; 6960</t>
+          <t>1332; 7696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1913; 10850</t>
+          <t>1881; 10764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11562; 32612</t>
+          <t>11709; 32540</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1836; 10702</t>
+          <t>1794; 10658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3641; 20880</t>
+          <t>6606; 19074</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>223863</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>244563</t>
+          <t>43361</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6419; 20996</t>
+          <t>6111; 21069</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7133; 21652</t>
+          <t>7818; 23242</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2899; 13462</t>
+          <t>2835; 12333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13318; 30383</t>
+          <t>14633; 31270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5125; 18736</t>
+          <t>5033; 17906</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10851; 29031</t>
+          <t>10734; 29195</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6897; 20434</t>
+          <t>6552; 20150</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20335; 517339</t>
+          <t>14656; 31180</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13236; 34040</t>
+          <t>13214; 31870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21229; 44336</t>
+          <t>21927; 45212</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11260; 28549</t>
+          <t>11798; 29680</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40187; 821809</t>
+          <t>32407; 56514</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>39418</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7236</t>
+          <t>818; 8148</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2974; 13995</t>
+          <t>2943; 13204</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5568; 20112</t>
+          <t>5368; 21653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7087; 20492</t>
+          <t>8475; 24134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>897; 9687</t>
+          <t>894; 8450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14715; 34567</t>
+          <t>13788; 32170</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11921; 31392</t>
+          <t>12306; 32003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14226; 30871</t>
+          <t>17645; 32611</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2568; 12701</t>
+          <t>2232; 12745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20200; 41290</t>
+          <t>20482; 42030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21650; 46870</t>
+          <t>21128; 45104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25352; 47538</t>
+          <t>29723; 52547</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26962</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>34559</t>
+          <t>41868</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2233; 14637</t>
+          <t>3019; 14595</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5081; 20488</t>
+          <t>5259; 21592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1950; 11660</t>
+          <t>1877; 10888</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3066; 17692</t>
+          <t>4944; 23303</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9313; 26892</t>
+          <t>9260; 26280</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13972; 32823</t>
+          <t>13104; 31413</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7978; 26060</t>
+          <t>8199; 26569</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19276; 37041</t>
+          <t>22209; 42735</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14671; 33879</t>
+          <t>13884; 33956</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21900; 47611</t>
+          <t>22477; 46932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12375; 30903</t>
+          <t>12164; 30594</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24203; 46742</t>
+          <t>29601; 57212</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68481</t>
+          <t>77073</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>297011</t>
+          <t>103189</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>365492</t>
+          <t>180262</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20049; 44031</t>
+          <t>19308; 43339</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48389; 82285</t>
+          <t>48686; 83993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21104; 44675</t>
+          <t>21443; 47395</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49750; 87329</t>
+          <t>60710; 96622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28013; 53119</t>
+          <t>28023; 52615</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58304; 92849</t>
+          <t>58557; 92714</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43997; 75424</t>
+          <t>44172; 76328</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91441; 916920</t>
+          <t>86677; 122575</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>53805; 86878</t>
+          <t>54699; 89303</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114187; 162529</t>
+          <t>114919; 162791</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70909; 110291</t>
+          <t>71436; 111975</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>156972; 1064040</t>
+          <t>156736; 207643</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
